--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61667797</v>
+        <v>103998341</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellan Nybräntberget och Överammer, Jmt</t>
+          <t>Nybränttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544360.8750560902</v>
+        <v>544509</v>
       </c>
       <c r="R2" t="n">
-        <v>7010410.933250657</v>
+        <v>7010440</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-06-06</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-06-06</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,52 +767,34 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103998381</v>
+        <v>61667795</v>
       </c>
       <c r="B3" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,34 +802,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219795</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nybränttjärnen, Jmt</t>
+          <t>Mellan Nybräntberget och Överammer, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544462.6062287771</v>
+        <v>544372</v>
       </c>
       <c r="R3" t="n">
-        <v>7010501.185073853</v>
+        <v>7010425</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:08</t>
+          <t>2016-06-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:08</t>
+          <t>2016-06-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,40 +876,30 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103998385</v>
+        <v>103998372</v>
       </c>
       <c r="B4" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,21 +907,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -970,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544506.4985814665</v>
+        <v>544460</v>
       </c>
       <c r="R4" t="n">
-        <v>7010429.626997599</v>
+        <v>7010507</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +976,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,15 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103998271</v>
+        <v>126728413</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,34 +1023,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nybränttjärnen, Jmt</t>
+          <t>Stamtjärnen, S, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544486.9472136878</v>
+        <v>544477</v>
       </c>
       <c r="R5" t="n">
-        <v>7010406.354922409</v>
+        <v>7010541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,22 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>08:42</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>08:42</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,40 +1093,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103998341</v>
+        <v>56220022</v>
       </c>
       <c r="B6" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,34 +1120,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nybränttjärnen, Jmt</t>
+          <t>Stamtjärn, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544509.5226038214</v>
+        <v>544464</v>
       </c>
       <c r="R6" t="n">
-        <v>7010439.591273834</v>
+        <v>7010553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,22 +1174,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:03</t>
+          <t>2014-11-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:03</t>
+          <t>2014-11-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,75 +1190,65 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103998333</v>
+        <v>61667797</v>
       </c>
       <c r="B7" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nybränttjärnen, Jmt</t>
+          <t>Mellan Nybräntberget och Överammer, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544508.9207407896</v>
+        <v>544361</v>
       </c>
       <c r="R7" t="n">
-        <v>7010385.008541587</v>
+        <v>7010411</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,22 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>08:57</t>
+          <t>2016-06-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>08:57</t>
+          <t>2016-06-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,39 +1292,47 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103998289</v>
+        <v>103998271</v>
       </c>
       <c r="B8" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,21 +1340,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1454,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544536.0959064778</v>
+        <v>544487</v>
       </c>
       <c r="R8" t="n">
-        <v>7010444.919285985</v>
+        <v>7010407</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1489,7 +1399,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1499,7 +1409,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1535,37 +1445,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103998307</v>
+        <v>103998206</v>
       </c>
       <c r="B9" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1575,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544451.5516239993</v>
+        <v>544441</v>
       </c>
       <c r="R9" t="n">
-        <v>7010516.818239448</v>
+        <v>7010395</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1610,7 +1515,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,7 +1525,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,6 +1536,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -1656,19 +1566,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103998206</v>
+        <v>126728410</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1692,14 +1597,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nybränttjärnen, Jmt</t>
+          <t>Stamtjärnen, S, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544441.0371506721</v>
+        <v>544477</v>
       </c>
       <c r="R10" t="n">
-        <v>7010394.897437416</v>
+        <v>7010541</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1726,22 +1631,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>08:37</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>08:37</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,45 +1647,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>61667795</v>
+        <v>103998385</v>
       </c>
       <c r="B11" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,38 +1674,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>504</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mellan Nybräntberget och Överammer, Jmt</t>
+          <t>Nybränttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544371.520212066</v>
+        <v>544507</v>
       </c>
       <c r="R11" t="n">
-        <v>7010425.061483855</v>
+        <v>7010430</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1856,22 +1728,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2016-06-06</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2016-06-06</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,57 +1754,57 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103998372</v>
+        <v>103998289</v>
       </c>
       <c r="B12" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>504</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1942,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544459.3646087007</v>
+        <v>544536</v>
       </c>
       <c r="R12" t="n">
-        <v>7010507.003595687</v>
+        <v>7010445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1987,7 +1859,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,6 +1888,1269 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126728412</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stamtjärnen, S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>544477</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7010541</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126728417</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stamtjärnen, S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>544496</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7010550</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126728411</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stamtjärnen, S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>544477</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7010541</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126728416</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stamtjärnen, S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>544496</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7010550</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>103998381</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nybränttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>544462</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7010501</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>103998415</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nybränttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>544505</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7010373</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126728420</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stamtjärnen, S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>544524</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7010558</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126728438</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stamtjärnen, S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>544548</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7010560</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>103998382</v>
+      </c>
+      <c r="B21" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nybränttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>544446</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7010552</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>56220024</v>
+      </c>
+      <c r="B22" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stamtjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>544510</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7010555</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2014-11-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2014-11-11</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>103998307</v>
+      </c>
+      <c r="B23" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nybränttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>544451</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7010517</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>103998333</v>
+      </c>
+      <c r="B24" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nybränttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>544509</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7010385</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3156,6 +3156,108 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126728422</v>
+      </c>
+      <c r="B25" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stamtjärnen, S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>544524</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7010558</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998341</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61667795</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998372</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126728413</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220022</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61667797</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998271</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998206</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,6 +1705,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126728410</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1776,6 +1826,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998385</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1892,6 +1947,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998289</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1989,6 +2049,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126728412</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2086,6 +2151,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126728417</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2183,6 +2253,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126728411</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2280,6 +2355,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126728416</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2396,6 +2476,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998381</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2512,6 +2597,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998415</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2609,6 +2699,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126728420</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2706,6 +2801,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126728438</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2822,6 +2922,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998382</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2923,6 +3028,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220024</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3039,6 +3149,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998307</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3153,6 +3268,11 @@
       <c r="AY24" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998333</t>
         </is>
       </c>
     </row>
@@ -3257,8 +3377,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126728422</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -3281,7 +3281,7 @@
         <v>126728422</v>
       </c>
       <c r="B25" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -3281,7 +3281,7 @@
         <v>126728422</v>
       </c>
       <c r="B25" t="n">
-        <v>100854</v>
+        <v>100881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3273,6 +3273,113 @@
       <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/103998333</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126728422</v>
+      </c>
+      <c r="B25" t="n">
+        <v>100886</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stamtjärnen, S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>544524</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7010558</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126728422</t>
         </is>
       </c>
     </row>
@@ -3301,6 +3408,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62948-2021 artfynd.xlsx
+++ b/artfynd/A 62948-2021 artfynd.xlsx
@@ -3281,7 +3281,7 @@
         <v>126728422</v>
       </c>
       <c r="B25" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
